--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,6 +920,654 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125490445</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56965</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Hult 1 våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>637966</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6521631</v>
+      </c>
+      <c r="S4" t="n">
+        <v>125</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>04:22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:42</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125490444</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56861</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102104</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Smådopping</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tachybaptus ruficollis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Hult 1 våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>637966</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6521631</v>
+      </c>
+      <c r="S5" t="n">
+        <v>125</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>04:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>04:42</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125490443</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56621</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Hult 1 våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>637966</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6521631</v>
+      </c>
+      <c r="S6" t="n">
+        <v>125</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>04:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>04:42</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125490442</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56604</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102106</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skedand</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spatula clypeata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Hult 1 våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>637966</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6521631</v>
+      </c>
+      <c r="S7" t="n">
+        <v>125</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>04:22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>04:42</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125490453</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57995</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Hult 1 våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>637966</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6521631</v>
+      </c>
+      <c r="S8" t="n">
+        <v>125</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>04:22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>04:42</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
         </is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125490445</v>
+        <v>125490444</v>
       </c>
       <c r="B4" t="n">
-        <v>56965</v>
+        <v>56880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,37 +939,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>102104</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Smådopping</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Tachybaptus ruficollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125490444</v>
+        <v>125490443</v>
       </c>
       <c r="B5" t="n">
-        <v>56861</v>
+        <v>56796</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,37 +1067,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102104</v>
+        <v>102932</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smådopping</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tachybaptus ruficollis</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1183,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125490443</v>
+        <v>125490445</v>
       </c>
       <c r="B6" t="n">
-        <v>56621</v>
+        <v>57053</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,25 +1199,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102932</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1222,14 +1226,10 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125490442</v>
+        <v>125490453</v>
       </c>
       <c r="B7" t="n">
-        <v>56604</v>
+        <v>58111</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,37 +1331,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102106</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skedand</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spatula clypeata</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1447,10 +1443,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125490453</v>
+        <v>125490442</v>
       </c>
       <c r="B8" t="n">
-        <v>57995</v>
+        <v>56779</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1463,33 +1459,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103018</v>
+        <v>102106</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Skedand</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spatula clypeata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125490444</v>
+        <v>125490443</v>
       </c>
       <c r="B4" t="n">
-        <v>56880</v>
+        <v>56796</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,37 +939,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102104</v>
+        <v>102932</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smådopping</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tachybaptus ruficollis</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1055,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125490443</v>
+        <v>125490453</v>
       </c>
       <c r="B5" t="n">
-        <v>56796</v>
+        <v>58111</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,41 +1071,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102932</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125490453</v>
+        <v>125490444</v>
       </c>
       <c r="B7" t="n">
-        <v>58111</v>
+        <v>56880</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>102104</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Smådopping</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tachybaptus ruficollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,6 +1568,134 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125677623</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58345</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nynäs NR, Hult 1 våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>637966</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6521631</v>
+      </c>
+      <c r="S9" t="n">
+        <v>125</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>05:04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
         </is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>125490453</v>
       </c>
       <c r="B6" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>125677623</v>
       </c>
       <c r="B9" t="n">
-        <v>58365</v>
+        <v>58366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>125490443</v>
       </c>
       <c r="B4" t="n">
-        <v>56806</v>
+        <v>56807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>125490442</v>
       </c>
       <c r="B5" t="n">
-        <v>56788</v>
+        <v>56789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>125490453</v>
       </c>
       <c r="B6" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>125490445</v>
       </c>
       <c r="B7" t="n">
-        <v>57063</v>
+        <v>57064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>125490444</v>
       </c>
       <c r="B8" t="n">
-        <v>56887</v>
+        <v>56888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>125677623</v>
       </c>
       <c r="B9" t="n">
-        <v>58366</v>
+        <v>58367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1553,7 +1553,7 @@
         <v>125677623</v>
       </c>
       <c r="B9" t="n">
-        <v>58367</v>
+        <v>58371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1670,6 +1670,122 @@
           <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128295454</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58210</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nynäs NR. Hultstugan norr våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>638006</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6521649</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1676,7 +1676,7 @@
         <v>128295454</v>
       </c>
       <c r="B10" t="n">
-        <v>58210</v>
+        <v>58211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1676,7 +1676,7 @@
         <v>128295454</v>
       </c>
       <c r="B10" t="n">
-        <v>58211</v>
+        <v>58223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1676,7 +1676,7 @@
         <v>128295454</v>
       </c>
       <c r="B10" t="n">
-        <v>58223</v>
+        <v>58227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1676,7 +1676,7 @@
         <v>128295454</v>
       </c>
       <c r="B10" t="n">
-        <v>58227</v>
+        <v>58254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>125490442</v>
       </c>
       <c r="B5" t="n">
-        <v>56961</v>
+        <v>56987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>125490442</v>
       </c>
       <c r="B5" t="n">
-        <v>56987</v>
+        <v>56989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>125490442</v>
       </c>
       <c r="B5" t="n">
-        <v>56989</v>
+        <v>56997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>125490442</v>
       </c>
       <c r="B5" t="n">
-        <v>56997</v>
+        <v>56998</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>125490444</v>
       </c>
       <c r="B8" t="n">
-        <v>56888</v>
+        <v>57121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>125490444</v>
       </c>
       <c r="B8" t="n">
-        <v>57121</v>
+        <v>57122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>125490444</v>
       </c>
       <c r="B8" t="n">
-        <v>57122</v>
+        <v>57125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>125490444</v>
       </c>
       <c r="B8" t="n">
-        <v>57125</v>
+        <v>57126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,6 +1786,248 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132321637</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58810</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nynäs NR. Hultstugan våtmark, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>638151</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6521621</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132321319</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58810</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nynäs NR. Hultstugan norra våtmark östra, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>637997</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6521581</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>132321637</v>
       </c>
       <c r="B11" t="n">
-        <v>58810</v>
+        <v>58811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>132321319</v>
       </c>
       <c r="B12" t="n">
-        <v>58810</v>
+        <v>58811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>132321637</v>
       </c>
       <c r="B11" t="n">
-        <v>58811</v>
+        <v>58815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>132321319</v>
       </c>
       <c r="B12" t="n">
-        <v>58811</v>
+        <v>58815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -1792,7 +1792,7 @@
         <v>132321637</v>
       </c>
       <c r="B11" t="n">
-        <v>58815</v>
+        <v>58816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>132321319</v>
       </c>
       <c r="B12" t="n">
-        <v>58815</v>
+        <v>58816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>68040838</v>
       </c>
       <c r="B2" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637771.8799128761</v>
+        <v>637772</v>
       </c>
       <c r="R2" t="n">
-        <v>6521475.749077281</v>
+        <v>6521476</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2017-10-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,49 +784,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109726847</v>
+        <v>125490443</v>
       </c>
       <c r="B3" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102976</v>
+        <v>102932</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -851,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637965.7829134935</v>
+        <v>637966</v>
       </c>
       <c r="R3" t="n">
-        <v>6521630.934865677</v>
+        <v>6521631</v>
       </c>
       <c r="S3" t="n">
         <v>125</v>
@@ -881,22 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>04:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:54</t>
+          <t>04:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,12 +895,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Örjan Jitelius</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Andersson</t>
+          <t>Örjan Jitelius</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -927,32 +911,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125490443</v>
+        <v>125490445</v>
       </c>
       <c r="B4" t="n">
-        <v>56807</v>
+        <v>57364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102932</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,14 +945,10 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1054,27 +1034,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125490442</v>
+        <v>109726847</v>
       </c>
       <c r="B5" t="n">
-        <v>57012</v>
+        <v>57774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102106</v>
+        <v>102976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skedand</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spatula clypeata</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1084,18 +1064,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1135,22 +1111,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>04:22</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>04:42</t>
+          <t>05:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,12 +1141,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Örjan Jitelius</t>
+          <t>Göran Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Örjan Jitelius</t>
+          <t>Göran Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1181,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125490453</v>
+        <v>125490454</v>
       </c>
       <c r="B6" t="n">
-        <v>58131</v>
+        <v>58541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,33 +1168,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>102987</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1304,27 +1280,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125490445</v>
+        <v>109726467</v>
       </c>
       <c r="B7" t="n">
-        <v>57064</v>
+        <v>58497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1334,14 +1310,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1381,22 +1357,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>04:22</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>04:42</t>
+          <t>05:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,12 +1387,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Örjan Jitelius</t>
+          <t>Göran Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Örjan Jitelius</t>
+          <t>Göran Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1427,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125490444</v>
+        <v>128295454</v>
       </c>
       <c r="B8" t="n">
-        <v>57146</v>
+        <v>58497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,49 +1414,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102104</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smådopping</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tachybaptus ruficollis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nynäs NR, Hult 1 våtmark, Srm</t>
+          <t>Nynäs NR. Hultstugan norr våtmark, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637966</v>
+        <v>638006</v>
       </c>
       <c r="R8" t="n">
-        <v>6521631</v>
+        <v>6521649</v>
       </c>
       <c r="S8" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1504,22 +1477,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>04:22</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>04:42</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,48 +1507,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Örjan Jitelius</t>
+          <t>Stephan Gäfvert</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Örjan Jitelius</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
-        </is>
-      </c>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125677623</v>
+        <v>125490453</v>
       </c>
       <c r="B9" t="n">
-        <v>58371</v>
+        <v>58439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>103018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1627,22 +1596,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>04:43</t>
+          <t>04:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>05:04</t>
+          <t>04:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,57 +1642,60 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128295454</v>
+        <v>125677623</v>
       </c>
       <c r="B10" t="n">
-        <v>58254</v>
+        <v>58676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nynäs NR. Hultstugan norr våtmark, Srm</t>
+          <t>Nynäs NR, Hult 1 våtmark, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638006</v>
+        <v>637966</v>
       </c>
       <c r="R10" t="n">
-        <v>6521649</v>
+        <v>6521631</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1747,22 +1719,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>04:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>05:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1777,22 +1749,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Stephan Gäfvert</t>
+          <t>Örjan Jitelius</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stephan Gäfvert</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Örjan Jitelius</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321637</v>
+        <v>132321319</v>
       </c>
       <c r="B11" t="n">
-        <v>58820</v>
+        <v>58837</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1795,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1829,14 +1805,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nynäs NR. Hultstugan våtmark, Srm</t>
+          <t>Nynäs NR. Hultstugan norra våtmark östra, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638151</v>
+        <v>637997</v>
       </c>
       <c r="R11" t="n">
-        <v>6521621</v>
+        <v>6521581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1868,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1878,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1910,10 +1886,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132321319</v>
+        <v>132321637</v>
       </c>
       <c r="B12" t="n">
-        <v>58820</v>
+        <v>58837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1950,14 +1926,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nynäs NR. Hultstugan norra våtmark östra, Srm</t>
+          <t>Nynäs NR. Hultstugan våtmark, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637997</v>
+        <v>638151</v>
       </c>
       <c r="R12" t="n">
-        <v>6521581</v>
+        <v>6521621</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1989,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1999,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 57006-2023 artfynd.xlsx
+++ b/artfynd/A 57006-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
           <t>Svampinventering 2017 ÅGP Sörmland</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68040838</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125490443</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
           <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125490445</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1154,6 +1174,11 @@
           <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109726847</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
           <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125490454</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1400,6 +1430,11 @@
           <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109726467</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1516,6 +1551,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128295454</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1639,6 +1679,11 @@
           <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125490453</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1762,6 +1807,11 @@
           <t>Små blivande våtmarker i Nynäs NR, Nyköping</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125677623</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1883,6 +1933,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321319</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2004,8 +2059,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>